--- a/grupos/3ARHM - Estadisticos 20211.xlsx
+++ b/grupos/3ARHM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -194,15 +194,15 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
@@ -227,289 +227,289 @@
     <t>ARROYO</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>NEPOMUCENO</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>SANDRIA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>TEPEPA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>LUIS YAEL</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>AISHA NAOMI</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>VANNIA GISELLE</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>IDETH JOSELYN</t>
+  </si>
+  <si>
+    <t>ESTHER ARISBETH</t>
+  </si>
+  <si>
+    <t>MONSERRATH YARETZY</t>
+  </si>
+  <si>
+    <t>ELELYN IVETH</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
     <t>CANSECO</t>
   </si>
   <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>HUESCA</t>
   </si>
   <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
     <t>MATA</t>
   </si>
   <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>NEPOMUCENO</t>
-  </si>
-  <si>
     <t>PARRA</t>
   </si>
   <si>
-    <t>PANZO</t>
-  </si>
-  <si>
     <t>QUIRIZ</t>
   </si>
   <si>
-    <t>REYES</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>SANDRIA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
   </si>
   <si>
     <t>DIAZ</t>
   </si>
   <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>LEAL</t>
   </si>
   <si>
     <t>TINOCO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ALONSO</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
+    <t>AGUILAR</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>TEPEPA</t>
+    <t>MELO</t>
   </si>
   <si>
     <t>VICTORIANO</t>
   </si>
   <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>LUIS YAEL</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
   </si>
   <si>
     <t>DINA BERENICE</t>
   </si>
   <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
     <t>ANGELA</t>
   </si>
   <si>
     <t>ANGELES NAHOMI</t>
   </si>
   <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
+    <t>ADRIANA ARELY</t>
+  </si>
+  <si>
+    <t>ARANTXA</t>
+  </si>
+  <si>
+    <t>MARIA YAZMIN</t>
+  </si>
+  <si>
+    <t>JAEL SAMAI</t>
+  </si>
+  <si>
+    <t>LIZBET</t>
   </si>
   <si>
     <t>ALDAIR OMAR</t>
   </si>
   <si>
+    <t>GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANIELA RUBI</t>
+  </si>
+  <si>
     <t>CRISTIAN ARTURO</t>
   </si>
   <si>
-    <t>VANNIA GISELLE</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
     <t>SUEMI</t>
   </si>
   <si>
-    <t>IDETH JOSELYN</t>
-  </si>
-  <si>
     <t>MONICA</t>
   </si>
   <si>
-    <t>ESTHER ARISBETH</t>
+    <t>JAROMI YAJAIRA</t>
+  </si>
+  <si>
+    <t>EDGAR RAMSES</t>
   </si>
   <si>
     <t>BERENICE</t>
   </si>
   <si>
-    <t>MONSERRATH YARETZY</t>
-  </si>
-  <si>
-    <t>ELELYN IVETH</t>
+    <t>IRIS VIANNEY</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
   </si>
   <si>
     <t>MARIAN</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>DEMUNER</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ALONSO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>ADRIANA ARELY</t>
-  </si>
-  <si>
-    <t>ARANTXA</t>
-  </si>
-  <si>
-    <t>MARIA YAZMIN</t>
-  </si>
-  <si>
-    <t>JAEL SAMAI</t>
-  </si>
-  <si>
-    <t>LIZBET</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANIELA RUBI</t>
-  </si>
-  <si>
-    <t>JAROMI YAJAIRA</t>
-  </si>
-  <si>
-    <t>EDGAR RAMSES</t>
-  </si>
-  <si>
-    <t>IRIS VIANNEY</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
   </si>
   <si>
     <t>AYARI</t>
@@ -1016,22 +1016,22 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1052,7 +1052,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -1061,7 +1061,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1102,13 +1102,13 @@
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1129,7 +1129,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -1138,13 +1138,13 @@
         <v>6</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1158,10 +1158,10 @@
         <v>-1</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>7</v>
@@ -1170,7 +1170,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1179,13 +1179,13 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1212,16 +1212,16 @@
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1253,16 +1253,16 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1312,7 +1312,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>10</v>
@@ -1333,13 +1333,13 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1366,16 +1366,16 @@
         <v>7</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1401,22 +1401,22 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1437,7 +1437,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>9</v>
@@ -1446,7 +1446,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1466,7 +1466,7 @@
         <v>10</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>8</v>
@@ -1478,7 +1478,7 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1487,13 +1487,13 @@
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1520,16 +1520,16 @@
         <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1537,7 +1537,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C11">
         <v>6</v>
@@ -1555,22 +1555,22 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1591,7 +1591,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>6</v>
@@ -1600,13 +1600,13 @@
         <v>6</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1632,22 +1632,22 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1683,7 +1683,7 @@
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1697,10 +1697,10 @@
         <v>-1</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F13">
         <v>6</v>
@@ -1718,13 +1718,13 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1751,16 +1751,16 @@
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1786,22 +1786,22 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1863,7 +1863,7 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1872,13 +1872,13 @@
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1940,22 +1940,22 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2017,22 +2017,22 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2082,10 +2082,10 @@
         <v>-1</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -2103,13 +2103,13 @@
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2136,16 +2136,16 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X18">
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2159,10 +2159,10 @@
         <v>6</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F19">
         <v>6</v>
@@ -2171,7 +2171,7 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2180,13 +2180,13 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2207,19 +2207,19 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>6</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2248,22 +2248,22 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2325,22 +2325,22 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2373,10 +2373,10 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2390,7 +2390,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>9</v>
@@ -2402,7 +2402,7 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2411,13 +2411,13 @@
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2444,13 +2444,13 @@
         <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2467,19 +2467,19 @@
         <v>-1</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F23">
         <v>6</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2488,13 +2488,13 @@
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2521,16 +2521,16 @@
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2544,10 +2544,10 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>6</v>
@@ -2565,10 +2565,10 @@
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2598,10 +2598,10 @@
         <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
         <v>6</v>
@@ -2615,22 +2615,22 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>-1</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F25">
         <v>5</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2642,13 +2642,13 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2669,22 +2669,22 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U25">
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2692,22 +2692,22 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C26">
         <v>-1</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F26">
         <v>5</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2719,13 +2719,13 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2746,22 +2746,22 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X26">
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2769,7 +2769,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C27">
         <v>6</v>
@@ -2796,13 +2796,13 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2823,7 +2823,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>6</v>
@@ -2835,10 +2835,10 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2852,7 +2852,7 @@
         <v>8</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E28">
         <v>8</v>
@@ -2873,13 +2873,13 @@
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2906,10 +2906,10 @@
         <v>8</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -2941,22 +2941,22 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2977,19 +2977,19 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>8</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>9</v>
@@ -3018,7 +3018,7 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3027,13 +3027,13 @@
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3054,7 +3054,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>7</v>
@@ -3063,13 +3063,13 @@
         <v>8</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3104,13 +3104,13 @@
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3146,7 +3146,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3172,7 +3172,7 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3181,13 +3181,13 @@
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3217,10 +3217,10 @@
         <v>6</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -3237,7 +3237,7 @@
         <v>10</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E33">
         <v>10</v>
@@ -3249,22 +3249,22 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3291,7 +3291,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3314,16 +3314,16 @@
         <v>-1</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F34">
         <v>6</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H34">
         <v>-1</v>
@@ -3335,13 +3335,13 @@
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3368,16 +3368,16 @@
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3409,16 +3409,16 @@
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3451,10 +3451,10 @@
         <v>8</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3468,7 +3468,7 @@
         <v>-1</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>6</v>
@@ -3489,13 +3489,13 @@
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3522,7 +3522,7 @@
         <v>-1</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>6</v>
@@ -3531,7 +3531,7 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3545,10 +3545,10 @@
         <v>6</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F37">
         <v>6</v>
@@ -3557,22 +3557,22 @@
         <v>6</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I37">
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3593,22 +3593,22 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U37">
         <v>6</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3634,7 +3634,7 @@
         <v>9</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -3643,13 +3643,13 @@
         <v>-1</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3670,7 +3670,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U38">
         <v>10</v>
@@ -3679,13 +3679,13 @@
         <v>8</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>10</v>
       </c>
       <c r="Y38">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3699,10 +3699,10 @@
         <v>-1</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F39">
         <v>7</v>
@@ -3720,13 +3720,13 @@
         <v>-1</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3753,16 +3753,16 @@
         <v>-1</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3827,30 +3827,30 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E2">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>66.67</v>
+      </c>
+      <c r="G2">
+        <v>33.33</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>52.78</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>7.7</v>
-      </c>
-      <c r="I2">
-        <v>17</v>
-      </c>
-      <c r="J2">
-        <v>47.22</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -3871,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="I3">
         <v>11</v>
@@ -3882,7 +3882,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -3891,30 +3891,30 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>69.44</v>
+        <v>75</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>30.56</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -3923,25 +3923,25 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>77.78</v>
+      </c>
+      <c r="G5">
+        <v>22.22</v>
+      </c>
+      <c r="H5">
+        <v>7.8</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>86.11</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>13.89</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3967,7 +3967,7 @@
         <v>13.89</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3987,25 +3987,25 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>91.67</v>
+      </c>
+      <c r="G7">
+        <v>8.33</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>88.89</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>8.1</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
-        <v>11.11</v>
       </c>
     </row>
   </sheetData>
@@ -4015,7 +4015,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4050,16 +4050,16 @@
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4070,33 +4070,33 @@
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920157</v>
+        <v>20330051920164</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>58</v>
@@ -4104,119 +4104,119 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920157</v>
+        <v>20330051920166</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920158</v>
+        <v>20330051920173</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920161</v>
+        <v>20330051920174</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920162</v>
+        <v>20330051920175</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920164</v>
+        <v>20330051920177</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920164</v>
+        <v>20330051920179</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>58</v>
@@ -4224,782 +4224,62 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920164</v>
+        <v>20330051920393</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920166</v>
+        <v>20330051920183</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920166</v>
+        <v>20330051920388</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920166</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" t="s">
-        <v>111</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920168</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920168</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920172</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920173</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920173</v>
-      </c>
-      <c r="B19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920173</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" t="s">
-        <v>114</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920173</v>
-      </c>
-      <c r="B21" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920174</v>
-      </c>
-      <c r="B22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22" t="s">
-        <v>115</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920174</v>
-      </c>
-      <c r="B23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" t="s">
-        <v>115</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920174</v>
-      </c>
-      <c r="B24" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920175</v>
-      </c>
-      <c r="B25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920175</v>
-      </c>
-      <c r="B26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" t="s">
-        <v>95</v>
-      </c>
-      <c r="D26" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920175</v>
-      </c>
-      <c r="B27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920175</v>
-      </c>
-      <c r="B28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" t="s">
-        <v>116</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920175</v>
-      </c>
-      <c r="B29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" t="s">
-        <v>95</v>
-      </c>
-      <c r="D29" t="s">
-        <v>116</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920306</v>
-      </c>
-      <c r="B30" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" t="s">
-        <v>96</v>
-      </c>
-      <c r="D30" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920177</v>
-      </c>
-      <c r="B31" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" t="s">
-        <v>97</v>
-      </c>
-      <c r="D31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920177</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" t="s">
-        <v>97</v>
-      </c>
-      <c r="D32" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920177</v>
-      </c>
-      <c r="B33" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" t="s">
-        <v>97</v>
-      </c>
-      <c r="D33" t="s">
-        <v>118</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920177</v>
-      </c>
-      <c r="B34" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" t="s">
-        <v>97</v>
-      </c>
-      <c r="D34" t="s">
-        <v>118</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920177</v>
-      </c>
-      <c r="B35" t="s">
-        <v>80</v>
-      </c>
-      <c r="C35" t="s">
-        <v>97</v>
-      </c>
-      <c r="D35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920178</v>
-      </c>
-      <c r="B36" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" t="s">
-        <v>119</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920179</v>
-      </c>
-      <c r="B37" t="s">
-        <v>82</v>
-      </c>
-      <c r="C37" t="s">
-        <v>99</v>
-      </c>
-      <c r="D37" t="s">
-        <v>120</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920254</v>
-      </c>
-      <c r="B38" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" t="s">
-        <v>100</v>
-      </c>
-      <c r="D38" t="s">
-        <v>121</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920393</v>
-      </c>
-      <c r="B39" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" t="s">
-        <v>101</v>
-      </c>
-      <c r="D39" t="s">
-        <v>122</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920393</v>
-      </c>
-      <c r="B40" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" t="s">
-        <v>101</v>
-      </c>
-      <c r="D40" t="s">
-        <v>122</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920393</v>
-      </c>
-      <c r="B41" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" t="s">
-        <v>101</v>
-      </c>
-      <c r="D41" t="s">
-        <v>122</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920393</v>
-      </c>
-      <c r="B42" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" t="s">
-        <v>101</v>
-      </c>
-      <c r="D42" t="s">
-        <v>122</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920183</v>
-      </c>
-      <c r="B43" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" t="s">
-        <v>102</v>
-      </c>
-      <c r="D43" t="s">
-        <v>123</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920183</v>
-      </c>
-      <c r="B44" t="s">
-        <v>85</v>
-      </c>
-      <c r="C44" t="s">
-        <v>102</v>
-      </c>
-      <c r="D44" t="s">
-        <v>123</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920184</v>
-      </c>
-      <c r="B45" t="s">
-        <v>85</v>
-      </c>
-      <c r="C45" t="s">
-        <v>103</v>
-      </c>
-      <c r="D45" t="s">
-        <v>124</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920184</v>
-      </c>
-      <c r="B46" t="s">
-        <v>85</v>
-      </c>
-      <c r="C46" t="s">
-        <v>103</v>
-      </c>
-      <c r="D46" t="s">
-        <v>124</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920388</v>
-      </c>
-      <c r="B47" t="s">
-        <v>86</v>
-      </c>
-      <c r="C47" t="s">
-        <v>104</v>
-      </c>
-      <c r="D47" t="s">
-        <v>125</v>
-      </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920388</v>
-      </c>
-      <c r="B48" t="s">
-        <v>86</v>
-      </c>
-      <c r="C48" t="s">
-        <v>104</v>
-      </c>
-      <c r="D48" t="s">
-        <v>125</v>
-      </c>
-      <c r="E48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920388</v>
-      </c>
-      <c r="B49" t="s">
-        <v>86</v>
-      </c>
-      <c r="C49" t="s">
-        <v>104</v>
-      </c>
-      <c r="D49" t="s">
-        <v>125</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -5035,172 +4315,172 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920175</v>
+        <v>20330051920156</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920177</v>
+        <v>20330051920157</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920173</v>
+        <v>20330051920164</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920393</v>
+        <v>20330051920166</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920157</v>
+        <v>20330051920173</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920164</v>
+        <v>20330051920174</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920166</v>
+        <v>20330051920175</v>
       </c>
       <c r="B8" t="s">
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920174</v>
+        <v>20330051920177</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920388</v>
+        <v>20330051920179</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920168</v>
+        <v>20330051920393</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5208,50 +4488,50 @@
         <v>20330051920183</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920184</v>
+        <v>20330051920388</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920156</v>
+        <v>20330051920368</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5259,146 +4539,146 @@
         <v>20330051920158</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920161</v>
+        <v>20330051920369</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920162</v>
+        <v>20330051920160</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920172</v>
+        <v>20330051920161</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920306</v>
+        <v>20330051920162</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920178</v>
+        <v>20330051920163</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920179</v>
+        <v>20330051920370</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920254</v>
+        <v>20330051920372</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D22" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920368</v>
+        <v>20330051920165</v>
       </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D23" t="s">
         <v>150</v>
@@ -5409,13 +4689,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920369</v>
+        <v>20330051920167</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D24" t="s">
         <v>151</v>
@@ -5426,13 +4706,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920160</v>
+        <v>20330051920168</v>
       </c>
       <c r="B25" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
         <v>152</v>
@@ -5443,13 +4723,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920163</v>
+        <v>20330051920371</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D26" t="s">
         <v>153</v>
@@ -5460,13 +4740,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920370</v>
+        <v>20330051920171</v>
       </c>
       <c r="B27" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D27" t="s">
         <v>154</v>
@@ -5477,13 +4757,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920372</v>
+        <v>20330051920172</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
         <v>155</v>
@@ -5494,13 +4774,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920165</v>
+        <v>20330051920306</v>
       </c>
       <c r="B29" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C29" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s">
         <v>156</v>
@@ -5511,13 +4791,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920167</v>
+        <v>20330051920178</v>
       </c>
       <c r="B30" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s">
         <v>157</v>
@@ -5528,13 +4808,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920371</v>
+        <v>20330051920180</v>
       </c>
       <c r="B31" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C31" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D31" t="s">
         <v>158</v>
@@ -5545,13 +4825,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920171</v>
+        <v>20330051920373</v>
       </c>
       <c r="B32" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="C32" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s">
         <v>159</v>
@@ -5562,13 +4842,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920180</v>
+        <v>20330051920254</v>
       </c>
       <c r="B33" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D33" t="s">
         <v>160</v>
@@ -5579,13 +4859,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920373</v>
+        <v>20330051920181</v>
       </c>
       <c r="B34" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s">
         <v>161</v>
@@ -5596,13 +4876,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920181</v>
+        <v>20330051920182</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="D35" t="s">
         <v>162</v>
@@ -5613,13 +4893,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20330051920182</v>
+        <v>20330051920184</v>
       </c>
       <c r="B36" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="C36" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D36" t="s">
         <v>163</v>
@@ -5633,10 +4913,10 @@
         <v>20330051920186</v>
       </c>
       <c r="B37" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D37" t="s">
         <v>164</v>
@@ -5652,7 +4932,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5684,114 +4964,114 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920162</v>
+        <v>20330051920174</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920162</v>
+        <v>20330051920174</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920168</v>
+        <v>20330051920306</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920168</v>
+        <v>20330051920306</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920184</v>
+        <v>20330051920156</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -5799,62 +5079,62 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920184</v>
+        <v>20330051920158</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="D7" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920156</v>
+        <v>20330051920161</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920158</v>
+        <v>20330051920172</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -5863,21 +5143,21 @@
         <v>57</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920161</v>
+        <v>20330051920178</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -5886,27 +5166,27 @@
         <v>57</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920172</v>
+        <v>20330051920179</v>
       </c>
       <c r="B11" t="s">
         <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -5914,93 +5194,24 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920306</v>
+        <v>20330051920393</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920178</v>
-      </c>
-      <c r="B13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" t="s">
-        <v>98</v>
-      </c>
-      <c r="D13" t="s">
-        <v>119</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920179</v>
-      </c>
-      <c r="B14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" t="s">
-        <v>120</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920254</v>
-      </c>
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" t="s">
-        <v>121</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3ARHM - Estadisticos 20211.xlsx
+++ b/grupos/3ARHM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -224,268 +224,268 @@
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>SANDRIA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>TEPEPA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>LUIS YAEL</t>
+  </si>
+  <si>
+    <t>AISHA NAOMI</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>VANNIA GISELLE</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>IDETH JOSELYN</t>
+  </si>
+  <si>
+    <t>ESTHER ARISBETH</t>
+  </si>
+  <si>
+    <t>MONSERRATH YARETZY</t>
+  </si>
+  <si>
+    <t>ELELYN IVETH</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
     <t>ARROYO</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MATA</t>
   </si>
   <si>
     <t>NEPOMUCENO</t>
   </si>
   <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SANDRIA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
   </si>
   <si>
     <t>MONTALVO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>LEAL</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ALONSO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
   </si>
   <si>
     <t>ALAMILLO</t>
   </si>
   <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>TEPEPA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>LUIS YAEL</t>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>VICTORIANO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
   </si>
   <si>
     <t>VICTOR HUGO</t>
   </si>
   <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>VANNIA GISELLE</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>ANGELES NAHOMI</t>
+  </si>
+  <si>
+    <t>ADRIANA ARELY</t>
+  </si>
+  <si>
+    <t>ARANTXA</t>
+  </si>
+  <si>
+    <t>MARIA YAZMIN</t>
+  </si>
+  <si>
+    <t>JAEL SAMAI</t>
+  </si>
+  <si>
+    <t>LIZBET</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANIELA RUBI</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
   </si>
   <si>
     <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>IDETH JOSELYN</t>
-  </si>
-  <si>
-    <t>ESTHER ARISBETH</t>
-  </si>
-  <si>
-    <t>MONSERRATH YARETZY</t>
-  </si>
-  <si>
-    <t>ELELYN IVETH</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>DEMUNER</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>LEAL</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ALONSO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>VICTORIANO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>ANGELES NAHOMI</t>
-  </si>
-  <si>
-    <t>ADRIANA ARELY</t>
-  </si>
-  <si>
-    <t>ARANTXA</t>
-  </si>
-  <si>
-    <t>MARIA YAZMIN</t>
-  </si>
-  <si>
-    <t>JAEL SAMAI</t>
-  </si>
-  <si>
-    <t>LIZBET</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANIELA RUBI</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
   </si>
   <si>
     <t>SUEMI</t>
@@ -1019,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>7</v>
@@ -1155,7 +1155,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1173,7 +1173,7 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1209,7 +1209,7 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -1250,7 +1250,7 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>7</v>
@@ -1327,7 +1327,7 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1404,7 +1404,7 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>7</v>
@@ -1481,7 +1481,7 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1635,7 +1635,7 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <v>8</v>
@@ -1789,7 +1789,7 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
         <v>9</v>
@@ -1866,7 +1866,7 @@
         <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1943,7 +1943,7 @@
         <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>9</v>
@@ -2020,7 +2020,7 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>8</v>
@@ -2174,7 +2174,7 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2210,7 +2210,7 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -2251,7 +2251,7 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>9</v>
@@ -2328,7 +2328,7 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
         <v>9</v>
@@ -2364,7 +2364,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2405,7 +2405,7 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2441,7 +2441,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2559,7 +2559,7 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -2618,7 +2618,7 @@
         <v>5</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>5</v>
@@ -2636,7 +2636,7 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -2672,7 +2672,7 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>5</v>
@@ -3021,7 +3021,7 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
         <v>-1</v>
@@ -3057,7 +3057,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>8</v>
@@ -3098,7 +3098,7 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
         <v>-1</v>
@@ -3134,7 +3134,7 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -3175,7 +3175,7 @@
         <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
         <v>-1</v>
@@ -3252,7 +3252,7 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
         <v>6</v>
@@ -3406,7 +3406,7 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J35">
         <v>6</v>
@@ -3560,7 +3560,7 @@
         <v>8</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
         <v>7</v>
@@ -3596,7 +3596,7 @@
         <v>8</v>
       </c>
       <c r="U37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V37">
         <v>7</v>
@@ -3637,7 +3637,7 @@
         <v>9</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J38">
         <v>-1</v>
@@ -3673,7 +3673,7 @@
         <v>8</v>
       </c>
       <c r="U38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V38">
         <v>8</v>
@@ -3859,25 +3859,25 @@
         <v>36</v>
       </c>
       <c r="D3">
+        <v>26</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>72.22</v>
+      </c>
+      <c r="G3">
+        <v>2.78</v>
+      </c>
+      <c r="H3">
+        <v>8.6</v>
+      </c>
+      <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
         <v>25</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>69.44</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>8.5</v>
-      </c>
-      <c r="I3">
-        <v>11</v>
-      </c>
-      <c r="J3">
-        <v>30.56</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4015,7 +4015,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4050,10 +4050,10 @@
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4064,16 +4064,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920157</v>
+        <v>20330051920164</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -4084,16 +4084,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920164</v>
+        <v>20330051920166</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4104,16 +4104,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920166</v>
+        <v>20330051920173</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -4124,27 +4124,27 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920173</v>
+        <v>20330051920174</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920174</v>
+        <v>20330051920177</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
@@ -4153,27 +4153,27 @@
         <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920175</v>
+        <v>20330051920179</v>
       </c>
       <c r="B8" t="s">
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -4184,16 +4184,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920177</v>
+        <v>20330051920393</v>
       </c>
       <c r="B9" t="s">
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -4204,16 +4204,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920179</v>
+        <v>20330051920183</v>
       </c>
       <c r="B10" t="s">
         <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4224,61 +4224,21 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920393</v>
+        <v>20330051920388</v>
       </c>
       <c r="B11" t="s">
         <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920183</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" t="s">
-        <v>99</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920388</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4321,10 +4281,10 @@
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -4332,16 +4292,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920157</v>
+        <v>20330051920164</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -4349,16 +4309,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920164</v>
+        <v>20330051920166</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -4366,16 +4326,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920166</v>
+        <v>20330051920173</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -4383,16 +4343,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920173</v>
+        <v>20330051920174</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -4400,7 +4360,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920174</v>
+        <v>20330051920177</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
@@ -4409,7 +4369,7 @@
         <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -4417,16 +4377,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920175</v>
+        <v>20330051920179</v>
       </c>
       <c r="B8" t="s">
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4434,16 +4394,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920177</v>
+        <v>20330051920393</v>
       </c>
       <c r="B9" t="s">
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4451,16 +4411,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920179</v>
+        <v>20330051920183</v>
       </c>
       <c r="B10" t="s">
         <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4468,16 +4428,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920393</v>
+        <v>20330051920388</v>
       </c>
       <c r="B11" t="s">
         <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4485,47 +4445,47 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920183</v>
+        <v>20330051920368</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920388</v>
+        <v>20330051920157</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920368</v>
+        <v>20330051920158</v>
       </c>
       <c r="B14" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
         <v>141</v>
@@ -4536,13 +4496,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920158</v>
+        <v>20330051920369</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
         <v>142</v>
@@ -4553,13 +4513,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920369</v>
+        <v>20330051920160</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D16" t="s">
         <v>143</v>
@@ -4570,13 +4530,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920160</v>
+        <v>20330051920161</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
         <v>144</v>
@@ -4587,13 +4547,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920161</v>
+        <v>20330051920162</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
         <v>145</v>
@@ -4604,13 +4564,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920162</v>
+        <v>20330051920163</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
         <v>146</v>
@@ -4621,13 +4581,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920163</v>
+        <v>20330051920370</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
         <v>147</v>
@@ -4638,13 +4598,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920370</v>
+        <v>20330051920372</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
         <v>148</v>
@@ -4655,13 +4615,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920372</v>
+        <v>20330051920165</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
         <v>149</v>
@@ -4672,13 +4632,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920165</v>
+        <v>20330051920167</v>
       </c>
       <c r="B23" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
         <v>150</v>
@@ -4689,13 +4649,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920167</v>
+        <v>20330051920168</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
         <v>151</v>
@@ -4706,13 +4666,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920168</v>
+        <v>20330051920371</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
         <v>152</v>
@@ -4723,13 +4683,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920371</v>
+        <v>20330051920171</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
         <v>153</v>
@@ -4740,13 +4700,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920171</v>
+        <v>20330051920172</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
         <v>154</v>
@@ -4757,13 +4717,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920172</v>
+        <v>20330051920175</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="D28" t="s">
         <v>155</v>
@@ -4777,10 +4737,10 @@
         <v>20330051920306</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
         <v>156</v>
@@ -4794,10 +4754,10 @@
         <v>20330051920178</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D30" t="s">
         <v>157</v>
@@ -4811,10 +4771,10 @@
         <v>20330051920180</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D31" t="s">
         <v>158</v>
@@ -4828,10 +4788,10 @@
         <v>20330051920373</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D32" t="s">
         <v>159</v>
@@ -4845,10 +4805,10 @@
         <v>20330051920254</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C33" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D33" t="s">
         <v>160</v>
@@ -4862,10 +4822,10 @@
         <v>20330051920181</v>
       </c>
       <c r="B34" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
         <v>161</v>
@@ -4879,10 +4839,10 @@
         <v>20330051920182</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D35" t="s">
         <v>162</v>
@@ -4896,10 +4856,10 @@
         <v>20330051920184</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C36" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
         <v>163</v>
@@ -4913,10 +4873,10 @@
         <v>20330051920186</v>
       </c>
       <c r="B37" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D37" t="s">
         <v>164</v>
@@ -4967,13 +4927,13 @@
         <v>20330051920174</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4990,13 +4950,13 @@
         <v>20330051920174</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5013,10 +4973,10 @@
         <v>20330051920306</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
         <v>156</v>
@@ -5036,10 +4996,10 @@
         <v>20330051920306</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
         <v>156</v>
@@ -5062,10 +5022,10 @@
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5082,13 +5042,13 @@
         <v>20330051920158</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -5105,13 +5065,13 @@
         <v>20330051920161</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5128,13 +5088,13 @@
         <v>20330051920172</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -5151,10 +5111,10 @@
         <v>20330051920178</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D10" t="s">
         <v>157</v>
@@ -5174,13 +5134,13 @@
         <v>20330051920179</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -5197,13 +5157,13 @@
         <v>20330051920393</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>

--- a/grupos/3ARHM - Estadisticos 20211.xlsx
+++ b/grupos/3ARHM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -194,15 +194,15 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
@@ -221,298 +221,298 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
     <t>MENDEZ</t>
   </si>
   <si>
-    <t>NAMORADO</t>
+    <t>NEPOMUCENO</t>
+  </si>
+  <si>
+    <t>PARRA</t>
   </si>
   <si>
     <t>PANZO</t>
   </si>
   <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>SANDRIA</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
     <t>ZUÑIGA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>LEAL</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ALONSO</t>
   </si>
   <si>
     <t>JERONIMO</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
     <t>MACARIO</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>MELO</t>
+  </si>
+  <si>
     <t>TEPEPA</t>
   </si>
   <si>
+    <t>VICTORIANO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
     <t>ROBLES</t>
   </si>
   <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
     <t>LUIS YAEL</t>
   </si>
   <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>ANGELES NAHOMI</t>
+  </si>
+  <si>
+    <t>ADRIANA ARELY</t>
+  </si>
+  <si>
     <t>AISHA NAOMI</t>
   </si>
   <si>
+    <t>ARANTXA</t>
+  </si>
+  <si>
+    <t>MARIA YAZMIN</t>
+  </si>
+  <si>
+    <t>JAEL SAMAI</t>
+  </si>
+  <si>
+    <t>LIZBET</t>
+  </si>
+  <si>
     <t>XIMENA</t>
   </si>
   <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANIELA RUBI</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
+  </si>
+  <si>
     <t>VANNIA GISELLE</t>
   </si>
   <si>
-    <t>LUZ ESTRELLA</t>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>SUEMI</t>
   </si>
   <si>
     <t>IDETH JOSELYN</t>
   </si>
   <si>
+    <t>MONICA</t>
+  </si>
+  <si>
     <t>ESTHER ARISBETH</t>
   </si>
   <si>
+    <t>JAROMI YAJAIRA</t>
+  </si>
+  <si>
+    <t>EDGAR RAMSES</t>
+  </si>
+  <si>
+    <t>BERENICE</t>
+  </si>
+  <si>
+    <t>IRIS VIANNEY</t>
+  </si>
+  <si>
     <t>MONSERRATH YARETZY</t>
   </si>
   <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
     <t>ELELYN IVETH</t>
   </si>
   <si>
+    <t>MARIAN</t>
+  </si>
+  <si>
+    <t>AYARI</t>
+  </si>
+  <si>
     <t>DANIELA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>DEMUNER</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>NEPOMUCENO</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>LEAL</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ALONSO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>VICTORIANO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>ANGELES NAHOMI</t>
-  </si>
-  <si>
-    <t>ADRIANA ARELY</t>
-  </si>
-  <si>
-    <t>ARANTXA</t>
-  </si>
-  <si>
-    <t>MARIA YAZMIN</t>
-  </si>
-  <si>
-    <t>JAEL SAMAI</t>
-  </si>
-  <si>
-    <t>LIZBET</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANIELA RUBI</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>SUEMI</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>JAROMI YAJAIRA</t>
-  </si>
-  <si>
-    <t>EDGAR RAMSES</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
-    <t>IRIS VIANNEY</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>MARIAN</t>
-  </si>
-  <si>
-    <t>AYARI</t>
   </si>
 </sst>
 </file>
@@ -1078,7 +1078,7 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -1096,7 +1096,7 @@
         <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -1132,7 +1132,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>6</v>
@@ -1558,7 +1558,7 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1594,7 +1594,7 @@
         <v>6</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -1694,7 +1694,7 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -1712,7 +1712,7 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1748,7 +1748,7 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1869,7 +1869,7 @@
         <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>10</v>
@@ -2079,7 +2079,7 @@
         <v>7</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>5</v>
@@ -2097,7 +2097,7 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -2133,7 +2133,7 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -2177,7 +2177,7 @@
         <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>8</v>
@@ -2408,7 +2408,7 @@
         <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>8</v>
@@ -2464,7 +2464,7 @@
         <v>8</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -2482,7 +2482,7 @@
         <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2518,7 +2518,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2695,7 +2695,7 @@
         <v>5</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D26">
         <v>5</v>
@@ -2713,7 +2713,7 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2749,7 +2749,7 @@
         <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V26">
         <v>5</v>
@@ -2790,7 +2790,7 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -2826,7 +2826,7 @@
         <v>5</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>7</v>
@@ -2867,7 +2867,7 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -2903,7 +2903,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>5</v>
@@ -2926,7 +2926,7 @@
         <v>8</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>8</v>
@@ -2944,7 +2944,7 @@
         <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>6</v>
@@ -2980,7 +2980,7 @@
         <v>9</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -3311,7 +3311,7 @@
         <v>8</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D34">
         <v>6</v>
@@ -3329,7 +3329,7 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3365,7 +3365,7 @@
         <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V34">
         <v>6</v>
@@ -3465,7 +3465,7 @@
         <v>8</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -3483,7 +3483,7 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
         <v>-1</v>
@@ -3519,7 +3519,7 @@
         <v>8</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V36">
         <v>5</v>
@@ -3696,7 +3696,7 @@
         <v>7</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -3714,7 +3714,7 @@
         <v>-1</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J39">
         <v>-1</v>
@@ -3750,7 +3750,7 @@
         <v>7</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V39">
         <v>5</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -3859,30 +3859,30 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>75</v>
+      </c>
+      <c r="G3">
+        <v>22.22</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
-      <c r="F3">
-        <v>72.22</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>2.78</v>
-      </c>
-      <c r="H3">
-        <v>8.6</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -3891,30 +3891,30 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4">
         <v>8</v>
       </c>
       <c r="F4">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="G4">
         <v>22.22</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -3923,19 +3923,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>77.78</v>
+        <v>83.33</v>
       </c>
       <c r="G5">
-        <v>22.22</v>
+        <v>16.67</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4015,7 +4015,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4044,201 +4044,21 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920156</v>
+        <v>20330051920174</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
         <v>69</v>
       </c>
-      <c r="D2" t="s">
-        <v>85</v>
-      </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920164</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920166</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920173</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920174</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920177</v>
-      </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920179</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920393</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920183</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920388</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4275,16 +4095,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920156</v>
+        <v>20330051920174</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
         <v>69</v>
-      </c>
-      <c r="D2" t="s">
-        <v>85</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -4292,166 +4112,166 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920164</v>
+        <v>20330051920368</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920166</v>
+        <v>20330051920156</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920173</v>
+        <v>20330051920157</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920174</v>
+        <v>20330051920158</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920177</v>
+        <v>20330051920369</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920179</v>
+        <v>20330051920160</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920393</v>
+        <v>20330051920161</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920183</v>
+        <v>20330051920162</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920388</v>
+        <v>20330051920163</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920368</v>
+        <v>20330051920164</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
         <v>139</v>
@@ -4462,13 +4282,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920157</v>
+        <v>20330051920370</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
         <v>140</v>
@@ -4479,13 +4299,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920158</v>
+        <v>20330051920372</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
         <v>141</v>
@@ -4496,13 +4316,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920369</v>
+        <v>20330051920165</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
         <v>142</v>
@@ -4513,13 +4333,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920160</v>
+        <v>20330051920167</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
         <v>143</v>
@@ -4530,13 +4350,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920161</v>
+        <v>20330051920166</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
         <v>144</v>
@@ -4547,13 +4367,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920162</v>
+        <v>20330051920168</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D18" t="s">
         <v>145</v>
@@ -4564,13 +4384,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920163</v>
+        <v>20330051920371</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D19" t="s">
         <v>146</v>
@@ -4581,13 +4401,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920370</v>
+        <v>20330051920171</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D20" t="s">
         <v>147</v>
@@ -4598,13 +4418,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920372</v>
+        <v>20330051920172</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
         <v>148</v>
@@ -4615,13 +4435,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920165</v>
+        <v>20330051920173</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
         <v>149</v>
@@ -4632,13 +4452,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920167</v>
+        <v>20330051920175</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
         <v>150</v>
@@ -4649,13 +4469,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920168</v>
+        <v>20330051920306</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
         <v>151</v>
@@ -4666,13 +4486,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920371</v>
+        <v>20330051920177</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
         <v>152</v>
@@ -4683,13 +4503,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920171</v>
+        <v>20330051920178</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
         <v>153</v>
@@ -4700,13 +4520,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920172</v>
+        <v>20330051920179</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
         <v>154</v>
@@ -4717,13 +4537,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920175</v>
+        <v>20330051920180</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
         <v>155</v>
@@ -4734,13 +4554,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920306</v>
+        <v>20330051920373</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
         <v>156</v>
@@ -4751,13 +4571,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920178</v>
+        <v>20330051920254</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D30" t="s">
         <v>157</v>
@@ -4768,13 +4588,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920180</v>
+        <v>20330051920181</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
         <v>158</v>
@@ -4785,13 +4605,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920373</v>
+        <v>20330051920393</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
         <v>159</v>
@@ -4802,13 +4622,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920254</v>
+        <v>20330051920182</v>
       </c>
       <c r="B33" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
         <v>160</v>
@@ -4819,13 +4639,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920181</v>
+        <v>20330051920183</v>
       </c>
       <c r="B34" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="D34" t="s">
         <v>161</v>
@@ -4836,13 +4656,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920182</v>
+        <v>20330051920184</v>
       </c>
       <c r="B35" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D35" t="s">
         <v>162</v>
@@ -4853,13 +4673,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>20330051920184</v>
+        <v>20330051920186</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D36" t="s">
         <v>163</v>
@@ -4870,13 +4690,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>20330051920186</v>
+        <v>20330051920388</v>
       </c>
       <c r="B37" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
         <v>164</v>
@@ -4892,7 +4712,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4927,19 +4747,19 @@
         <v>20330051920174</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4950,19 +4770,19 @@
         <v>20330051920174</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -4970,22 +4790,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920306</v>
+        <v>20330051920158</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4993,22 +4813,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920306</v>
+        <v>20330051920161</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5016,39 +4836,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920156</v>
+        <v>20330051920172</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>148</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920158</v>
+        <v>20330051920178</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
         <v>120</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -5058,121 +4878,6 @@
       </c>
       <c r="G7">
         <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920161</v>
-      </c>
-      <c r="B8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" t="s">
-        <v>144</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920172</v>
-      </c>
-      <c r="B9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" t="s">
-        <v>154</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920178</v>
-      </c>
-      <c r="B10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C10" t="s">
-        <v>133</v>
-      </c>
-      <c r="D10" t="s">
-        <v>157</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920179</v>
-      </c>
-      <c r="B11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920393</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/3ARHM - Estadisticos 20211.xlsx
+++ b/grupos/3ARHM - Estadisticos 20211.xlsx
@@ -3095,7 +3095,7 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I31">
         <v>9</v>
@@ -3403,7 +3403,7 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I35">
         <v>7</v>

--- a/grupos/3ARHM - Estadisticos 20211.xlsx
+++ b/grupos/3ARHM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -194,10 +194,13 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
+    <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
     <t>Martínez López Miguel Ángel</t>
@@ -206,9 +209,6 @@
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -221,253 +221,253 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DEMUNER</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
     <t>NAMORADO</t>
   </si>
   <si>
+    <t>NEPOMUCENO</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANDRIA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>LEAL</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ALONSO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>TEPEPA</t>
+  </si>
+  <si>
+    <t>VICTORIANO</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>LUIS YAEL</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>ANGELES NAHOMI</t>
+  </si>
+  <si>
+    <t>ADRIANA ARELY</t>
+  </si>
+  <si>
+    <t>AISHA NAOMI</t>
+  </si>
+  <si>
+    <t>ARANTXA</t>
+  </si>
+  <si>
+    <t>MARIA YAZMIN</t>
+  </si>
+  <si>
+    <t>JAEL SAMAI</t>
+  </si>
+  <si>
+    <t>LIZBET</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANIELA RUBI</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
+  </si>
+  <si>
+    <t>VANNIA GISELLE</t>
+  </si>
+  <si>
     <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DEMUNER</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>NEPOMUCENO</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANDRIA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>LEAL</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ALONSO</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>TEPEPA</t>
-  </si>
-  <si>
-    <t>VICTORIANO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>LUIS YAEL</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>ANGELES NAHOMI</t>
-  </si>
-  <si>
-    <t>ADRIANA ARELY</t>
-  </si>
-  <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>ARANTXA</t>
-  </si>
-  <si>
-    <t>MARIA YAZMIN</t>
-  </si>
-  <si>
-    <t>JAEL SAMAI</t>
-  </si>
-  <si>
-    <t>LIZBET</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANIELA RUBI</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
-  </si>
-  <si>
-    <t>VANNIA GISELLE</t>
   </si>
   <si>
     <t>ABIGAIL</t>
@@ -1034,22 +1034,22 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -1058,7 +1058,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -1099,7 +1099,7 @@
         <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>9</v>
@@ -1111,40 +1111,40 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>6</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1176,7 +1176,7 @@
         <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>5</v>
@@ -1188,31 +1188,31 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>7</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>5</v>
@@ -1221,7 +1221,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1247,7 +1247,7 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>10</v>
@@ -1265,25 +1265,25 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>10</v>
@@ -1292,7 +1292,7 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1324,13 +1324,13 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
         <v>5</v>
@@ -1342,40 +1342,40 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>5</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1419,22 +1419,22 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1452,7 +1452,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1484,7 +1484,7 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>6</v>
@@ -1496,22 +1496,22 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1520,10 +1520,10 @@
         <v>10</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>8</v>
@@ -1573,40 +1573,40 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1650,22 +1650,22 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1674,7 +1674,7 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1709,13 +1709,13 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
         <v>5</v>
@@ -1727,28 +1727,28 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1804,22 +1804,22 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1881,28 +1881,28 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>9</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -1958,22 +1958,22 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -2035,22 +2035,22 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -2059,7 +2059,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -2094,13 +2094,13 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>5</v>
@@ -2112,40 +2112,40 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>5</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2189,22 +2189,22 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -2219,7 +2219,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2266,22 +2266,22 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2290,7 +2290,7 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2343,22 +2343,22 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2420,34 +2420,34 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2485,7 +2485,7 @@
         <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>5</v>
@@ -2497,28 +2497,28 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2527,7 +2527,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2553,16 +2553,16 @@
         <v>6</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>5</v>
@@ -2571,34 +2571,34 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>7</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2607,7 +2607,7 @@
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2633,13 +2633,13 @@
         <v>5</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>5</v>
@@ -2651,22 +2651,22 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
         <v>5</v>
@@ -2710,13 +2710,13 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>5</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>5</v>
@@ -2728,22 +2728,22 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
         <v>5</v>
@@ -2787,13 +2787,13 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>7</v>
@@ -2805,40 +2805,40 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
         <v>5</v>
       </c>
       <c r="U27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2864,13 +2864,13 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
         <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>5</v>
@@ -2882,28 +2882,28 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>5</v>
@@ -2912,7 +2912,7 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -2959,22 +2959,22 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -2983,7 +2983,7 @@
         <v>6</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -3024,7 +3024,7 @@
         <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
         <v>7</v>
@@ -3036,22 +3036,22 @@
         <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>8</v>
@@ -3060,7 +3060,7 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3101,7 +3101,7 @@
         <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
         <v>7</v>
@@ -3113,34 +3113,34 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T31">
         <v>8</v>
       </c>
       <c r="U31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>9</v>
@@ -3178,7 +3178,7 @@
         <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
         <v>10</v>
@@ -3190,34 +3190,34 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
         <v>9</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V32">
         <v>6</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3267,34 +3267,34 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>9</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>6</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3326,13 +3326,13 @@
         <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <v>8</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>7</v>
@@ -3344,25 +3344,25 @@
         <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>7</v>
@@ -3371,13 +3371,13 @@
         <v>6</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3421,22 +3421,22 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>8</v>
@@ -3445,10 +3445,10 @@
         <v>8</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>9</v>
@@ -3480,13 +3480,13 @@
         <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I36">
         <v>7</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
         <v>6</v>
@@ -3498,25 +3498,25 @@
         <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U36">
         <v>6</v>
@@ -3525,13 +3525,13 @@
         <v>5</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3575,22 +3575,22 @@
         <v>8</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T37">
         <v>8</v>
@@ -3599,10 +3599,10 @@
         <v>8</v>
       </c>
       <c r="V37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X37">
         <v>6</v>
@@ -3640,7 +3640,7 @@
         <v>8</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K38">
         <v>6</v>
@@ -3652,22 +3652,22 @@
         <v>7</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T38">
         <v>8</v>
@@ -3676,13 +3676,13 @@
         <v>9</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y38">
         <v>8</v>
@@ -3711,13 +3711,13 @@
         <v>6</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I39">
         <v>5</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K39">
         <v>5</v>
@@ -3729,25 +3729,25 @@
         <v>5</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U39">
         <v>6</v>
@@ -3827,19 +3827,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>66.67</v>
+        <v>69.44</v>
       </c>
       <c r="G2">
-        <v>33.33</v>
+        <v>30.56</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -3859,13 +3859,13 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3">
         <v>8</v>
       </c>
       <c r="F3">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="G3">
         <v>22.22</v>
@@ -3874,15 +3874,15 @@
         <v>7.5</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -3891,19 +3891,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>77.78</v>
+        <v>80.56</v>
       </c>
       <c r="G4">
-        <v>22.22</v>
+        <v>19.44</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -3923,19 +3923,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>83.33</v>
+        <v>86.11</v>
       </c>
       <c r="G5">
-        <v>16.67</v>
+        <v>13.89</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3946,7 +3946,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
@@ -3955,19 +3955,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>86.11</v>
+        <v>91.67</v>
       </c>
       <c r="G6">
-        <v>13.89</v>
+        <v>8.33</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3978,7 +3978,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
@@ -3987,19 +3987,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>91.67</v>
+        <v>94.44</v>
       </c>
       <c r="G7">
-        <v>8.33</v>
+        <v>5.56</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4015,7 +4015,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4040,26 +4040,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920174</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -4095,30 +4075,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920174</v>
+        <v>20330051920368</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920368</v>
+        <v>20330051920156</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
         <v>130</v>
@@ -4129,13 +4109,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920156</v>
+        <v>20330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
         <v>131</v>
@@ -4146,13 +4126,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920157</v>
+        <v>20330051920158</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
         <v>132</v>
@@ -4163,13 +4143,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920158</v>
+        <v>20330051920369</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
         <v>133</v>
@@ -4180,13 +4160,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920369</v>
+        <v>20330051920160</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
         <v>134</v>
@@ -4197,13 +4177,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920160</v>
+        <v>20330051920161</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
         <v>135</v>
@@ -4214,13 +4194,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920161</v>
+        <v>20330051920162</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
         <v>136</v>
@@ -4231,13 +4211,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920162</v>
+        <v>20330051920163</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
         <v>137</v>
@@ -4248,13 +4228,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920163</v>
+        <v>20330051920164</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
         <v>138</v>
@@ -4265,13 +4245,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920164</v>
+        <v>20330051920370</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
         <v>139</v>
@@ -4282,10 +4262,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920370</v>
+        <v>20330051920372</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
         <v>109</v>
@@ -4299,10 +4279,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920372</v>
+        <v>20330051920165</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
         <v>110</v>
@@ -4316,10 +4296,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920165</v>
+        <v>20330051920167</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
         <v>111</v>
@@ -4333,10 +4313,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920167</v>
+        <v>20330051920166</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
         <v>112</v>
@@ -4350,10 +4330,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920166</v>
+        <v>20330051920168</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
         <v>113</v>
@@ -4367,10 +4347,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920168</v>
+        <v>20330051920371</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
         <v>114</v>
@@ -4384,10 +4364,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920371</v>
+        <v>20330051920171</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
         <v>115</v>
@@ -4401,13 +4381,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920171</v>
+        <v>20330051920172</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
         <v>147</v>
@@ -4418,13 +4398,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920172</v>
+        <v>20330051920173</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
         <v>148</v>
@@ -4435,13 +4415,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920173</v>
+        <v>20330051920174</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
         <v>149</v>
@@ -4455,10 +4435,10 @@
         <v>20330051920175</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
         <v>150</v>
@@ -4472,10 +4452,10 @@
         <v>20330051920306</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
         <v>151</v>
@@ -4489,10 +4469,10 @@
         <v>20330051920177</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
         <v>152</v>
@@ -4506,10 +4486,10 @@
         <v>20330051920178</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
         <v>153</v>
@@ -4523,10 +4503,10 @@
         <v>20330051920179</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
         <v>154</v>
@@ -4540,10 +4520,10 @@
         <v>20330051920180</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
         <v>155</v>
@@ -4557,10 +4537,10 @@
         <v>20330051920373</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
         <v>156</v>
@@ -4574,10 +4554,10 @@
         <v>20330051920254</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D30" t="s">
         <v>157</v>
@@ -4591,10 +4571,10 @@
         <v>20330051920181</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D31" t="s">
         <v>158</v>
@@ -4608,10 +4588,10 @@
         <v>20330051920393</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
         <v>159</v>
@@ -4625,10 +4605,10 @@
         <v>20330051920182</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D33" t="s">
         <v>160</v>
@@ -4642,10 +4622,10 @@
         <v>20330051920183</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D34" t="s">
         <v>161</v>
@@ -4659,10 +4639,10 @@
         <v>20330051920184</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D35" t="s">
         <v>162</v>
@@ -4676,10 +4656,10 @@
         <v>20330051920186</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D36" t="s">
         <v>163</v>
@@ -4693,10 +4673,10 @@
         <v>20330051920388</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D37" t="s">
         <v>164</v>
@@ -4712,7 +4692,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4744,22 +4724,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920174</v>
+        <v>20330051920183</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4767,45 +4747,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920174</v>
+        <v>20330051920183</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>58</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920158</v>
+        <v>20330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4813,16 +4793,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920161</v>
+        <v>20330051920158</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -4836,16 +4816,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920172</v>
+        <v>20330051920162</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -4859,24 +4839,70 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
+        <v>20330051920306</v>
+      </c>
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
         <v>20330051920178</v>
       </c>
-      <c r="B7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="B8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" t="s">
         <v>153</v>
       </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
         <v>57</v>
       </c>
-      <c r="G7">
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920181</v>
+      </c>
+      <c r="B9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" t="s">
+        <v>158</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHM - Estadisticos 20211.xlsx
+++ b/grupos/3ARHM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -3211,7 +3211,7 @@
         <v>9</v>
       </c>
       <c r="U32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>6</v>
@@ -3955,19 +3955,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>91.67</v>
+        <v>94.44</v>
       </c>
       <c r="G6">
-        <v>8.33</v>
+        <v>5.56</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4692,7 +4692,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4883,29 +4883,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920181</v>
-      </c>
-      <c r="B9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" t="s">
-        <v>158</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
